--- a/win5_cards_export/race_cards.xlsx
+++ b/win5_cards_export/race_cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\git\horse_racing\HorseRacing\win5_cards_export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\02_programs\01_horse_racing\HorseRacing\win5_cards_export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A353B505-F211-4C48-899C-793CC75AED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA755F0-65C7-4FBB-B279-0C3FBA3F525B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{F5095F6D-2853-4445-8829-8A6709F94A0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{F5095F6D-2853-4445-8829-8A6709F94A0F}"/>
   </bookViews>
   <sheets>
     <sheet name="WIN５ (馬名) (1222_1)" sheetId="46" state="hidden" r:id="rId1"/>
@@ -1077,7 +1077,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1302,12 +1302,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
       <sz val="24"/>
       <name val="Yu Gothic"/>
@@ -2761,7 +2755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -3136,7 +3130,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3178,19 +3172,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="24" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3211,7 +3205,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3238,10 +3232,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="34" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3250,10 +3244,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="34" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3270,6 +3264,165 @@
     </xf>
     <xf numFmtId="176" fontId="24" fillId="0" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="28" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="28" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="28" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="28" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="28" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="27" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3289,202 +3442,34 @@
     <xf numFmtId="20" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="27" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="28" fillId="0" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="28" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="28" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="28" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="28" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -4092,31 +4077,31 @@
     </row>
     <row r="3" spans="1:21" s="23" customFormat="1" ht="24.75" customHeight="1" thickBot="1">
       <c r="A3" s="22"/>
-      <c r="B3" s="240" t="s">
+      <c r="B3" s="243" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="241"/>
       <c r="D3" s="241"/>
       <c r="E3" s="242"/>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="243" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="241"/>
       <c r="H3" s="241"/>
       <c r="I3" s="242"/>
-      <c r="J3" s="240" t="s">
+      <c r="J3" s="243" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="241"/>
       <c r="L3" s="241"/>
       <c r="M3" s="242"/>
-      <c r="N3" s="240" t="s">
+      <c r="N3" s="243" t="s">
         <v>53</v>
       </c>
       <c r="O3" s="241"/>
       <c r="P3" s="241"/>
       <c r="Q3" s="241"/>
-      <c r="R3" s="240" t="s">
+      <c r="R3" s="243" t="s">
         <v>18</v>
       </c>
       <c r="S3" s="241"/>
@@ -4125,31 +4110,31 @@
     </row>
     <row r="4" spans="1:21" s="23" customFormat="1" ht="24.75" customHeight="1" thickBot="1">
       <c r="A4" s="22"/>
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="240" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="241"/>
       <c r="D4" s="241"/>
       <c r="E4" s="242"/>
-      <c r="F4" s="243" t="s">
+      <c r="F4" s="240" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="241"/>
       <c r="H4" s="241"/>
       <c r="I4" s="242"/>
-      <c r="J4" s="243" t="s">
+      <c r="J4" s="240" t="s">
         <v>55</v>
       </c>
       <c r="K4" s="241"/>
       <c r="L4" s="241"/>
       <c r="M4" s="242"/>
-      <c r="N4" s="243" t="s">
+      <c r="N4" s="240" t="s">
         <v>54</v>
       </c>
       <c r="O4" s="241"/>
       <c r="P4" s="241"/>
       <c r="Q4" s="241"/>
-      <c r="R4" s="243" t="s">
+      <c r="R4" s="240" t="s">
         <v>102</v>
       </c>
       <c r="S4" s="241"/>
@@ -5040,16 +5025,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:U3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="N4:Q4"/>
     <mergeCell ref="R4:U4"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:U3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C6:D23">
@@ -5134,18 +5119,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" ht="39" customHeight="1" thickBot="1">
-      <c r="A1" s="227"/>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
+      <c r="A1" s="191"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
       <c r="F1" s="103"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
       <c r="M1" s="67"/>
       <c r="N1" s="67"/>
       <c r="O1" s="67"/>
@@ -5153,10 +5138,10 @@
       <c r="Q1" s="67"/>
       <c r="R1" s="67"/>
       <c r="S1" s="67"/>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
-      <c r="W1" s="228"/>
+      <c r="T1" s="192"/>
+      <c r="U1" s="192"/>
+      <c r="V1" s="192"/>
+      <c r="W1" s="192"/>
       <c r="X1" s="67"/>
       <c r="Y1" s="67"/>
       <c r="Z1" s="67"/>
@@ -5199,30 +5184,30 @@
       <c r="BI1" s="67"/>
     </row>
     <row r="2" spans="1:65" ht="54.75" customHeight="1" thickBot="1">
-      <c r="A2" s="224" t="s">
+      <c r="A2" s="185" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="225"/>
-      <c r="C2" s="225"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="237">
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
+      <c r="E2" s="187"/>
+      <c r="F2" s="181">
         <f ca="1">NOW()</f>
-        <v>46145.644363194442</v>
-      </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="235" t="s">
+        <v>46217.416346874998</v>
+      </c>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="182"/>
+      <c r="K2" s="182"/>
+      <c r="L2" s="182"/>
+      <c r="M2" s="182"/>
+      <c r="N2" s="183"/>
+      <c r="O2" s="175" t="s">
         <v>146</v>
       </c>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
+      <c r="P2" s="176"/>
+      <c r="Q2" s="176"/>
       <c r="R2" s="67"/>
       <c r="S2" s="67"/>
       <c r="T2" s="102"/>
@@ -5270,13 +5255,13 @@
     </row>
     <row r="3" spans="1:65" s="21" customFormat="1" ht="47.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="55"/>
-      <c r="B3" s="229" t="s">
+      <c r="B3" s="193" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="230"/>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="231"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="194"/>
+      <c r="F3" s="195"/>
       <c r="G3" s="70">
         <v>1</v>
       </c>
@@ -5290,13 +5275,13 @@
       <c r="K3" s="71"/>
       <c r="L3" s="71"/>
       <c r="M3" s="72"/>
-      <c r="N3" s="229" t="s">
+      <c r="N3" s="193" t="s">
         <v>140</v>
       </c>
-      <c r="O3" s="230"/>
-      <c r="P3" s="230"/>
-      <c r="Q3" s="230"/>
-      <c r="R3" s="231"/>
+      <c r="O3" s="194"/>
+      <c r="P3" s="194"/>
+      <c r="Q3" s="194"/>
+      <c r="R3" s="195"/>
       <c r="S3" s="70">
         <v>1</v>
       </c>
@@ -5318,13 +5303,13 @@
       <c r="Y3" s="72">
         <v>7</v>
       </c>
-      <c r="Z3" s="229" t="s">
+      <c r="Z3" s="193" t="s">
         <v>141</v>
       </c>
-      <c r="AA3" s="230"/>
-      <c r="AB3" s="230"/>
-      <c r="AC3" s="230"/>
-      <c r="AD3" s="231"/>
+      <c r="AA3" s="194"/>
+      <c r="AB3" s="194"/>
+      <c r="AC3" s="194"/>
+      <c r="AD3" s="195"/>
       <c r="AE3" s="70">
         <v>1</v>
       </c>
@@ -5346,13 +5331,13 @@
       <c r="AK3" s="72">
         <v>7</v>
       </c>
-      <c r="AL3" s="229" t="s">
+      <c r="AL3" s="193" t="s">
         <v>142</v>
       </c>
-      <c r="AM3" s="230"/>
-      <c r="AN3" s="230"/>
-      <c r="AO3" s="230"/>
-      <c r="AP3" s="231"/>
+      <c r="AM3" s="194"/>
+      <c r="AN3" s="194"/>
+      <c r="AO3" s="194"/>
+      <c r="AP3" s="195"/>
       <c r="AQ3" s="70">
         <v>1</v>
       </c>
@@ -5374,13 +5359,13 @@
       <c r="AW3" s="72">
         <v>7</v>
       </c>
-      <c r="AX3" s="229" t="s">
+      <c r="AX3" s="193" t="s">
         <v>143</v>
       </c>
-      <c r="AY3" s="230"/>
-      <c r="AZ3" s="230"/>
-      <c r="BA3" s="230"/>
-      <c r="BB3" s="231"/>
+      <c r="AY3" s="194"/>
+      <c r="AZ3" s="194"/>
+      <c r="BA3" s="194"/>
+      <c r="BB3" s="195"/>
       <c r="BC3" s="70">
         <v>1</v>
       </c>
@@ -5404,228 +5389,228 @@
       </c>
     </row>
     <row r="4" spans="1:65" s="23" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A4" s="232" t="s">
+      <c r="A4" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="178"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="218" t="s">
+      <c r="B4" s="231"/>
+      <c r="C4" s="232"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="215"/>
-      <c r="K4" s="215"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="178"/>
-      <c r="O4" s="179"/>
-      <c r="P4" s="179"/>
-      <c r="Q4" s="179"/>
-      <c r="R4" s="180"/>
-      <c r="S4" s="218" t="s">
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
+      <c r="L4" s="179"/>
+      <c r="M4" s="200"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="233"/>
+      <c r="S4" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="T4" s="215" t="s">
+      <c r="T4" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="U4" s="215" t="s">
+      <c r="U4" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="V4" s="215"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="215"/>
-      <c r="Y4" s="220"/>
-      <c r="Z4" s="178"/>
-      <c r="AA4" s="179"/>
-      <c r="AB4" s="179"/>
-      <c r="AC4" s="179"/>
-      <c r="AD4" s="180"/>
-      <c r="AE4" s="218" t="s">
+      <c r="V4" s="179"/>
+      <c r="W4" s="179"/>
+      <c r="X4" s="179"/>
+      <c r="Y4" s="200"/>
+      <c r="Z4" s="231"/>
+      <c r="AA4" s="232"/>
+      <c r="AB4" s="232"/>
+      <c r="AC4" s="232"/>
+      <c r="AD4" s="233"/>
+      <c r="AE4" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="AF4" s="215" t="s">
+      <c r="AF4" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="AG4" s="215" t="s">
+      <c r="AG4" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="AH4" s="215"/>
-      <c r="AI4" s="215"/>
-      <c r="AJ4" s="215"/>
-      <c r="AK4" s="220"/>
-      <c r="AL4" s="244"/>
-      <c r="AM4" s="245"/>
-      <c r="AN4" s="245"/>
-      <c r="AO4" s="245"/>
-      <c r="AP4" s="246"/>
-      <c r="AQ4" s="218" t="s">
+      <c r="AH4" s="179"/>
+      <c r="AI4" s="179"/>
+      <c r="AJ4" s="179"/>
+      <c r="AK4" s="200"/>
+      <c r="AL4" s="237"/>
+      <c r="AM4" s="238"/>
+      <c r="AN4" s="238"/>
+      <c r="AO4" s="238"/>
+      <c r="AP4" s="239"/>
+      <c r="AQ4" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="AR4" s="215" t="s">
+      <c r="AR4" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="AS4" s="215" t="s">
+      <c r="AS4" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="AT4" s="215"/>
-      <c r="AU4" s="215"/>
-      <c r="AV4" s="215"/>
-      <c r="AW4" s="220"/>
-      <c r="AX4" s="178"/>
-      <c r="AY4" s="179"/>
-      <c r="AZ4" s="179"/>
-      <c r="BA4" s="179"/>
-      <c r="BB4" s="180"/>
-      <c r="BC4" s="218" t="s">
+      <c r="AT4" s="179"/>
+      <c r="AU4" s="179"/>
+      <c r="AV4" s="179"/>
+      <c r="AW4" s="200"/>
+      <c r="AX4" s="231"/>
+      <c r="AY4" s="232"/>
+      <c r="AZ4" s="232"/>
+      <c r="BA4" s="232"/>
+      <c r="BB4" s="233"/>
+      <c r="BC4" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="BD4" s="215" t="s">
+      <c r="BD4" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="BE4" s="215" t="s">
+      <c r="BE4" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="BF4" s="215"/>
-      <c r="BG4" s="215"/>
-      <c r="BH4" s="215"/>
-      <c r="BI4" s="220"/>
+      <c r="BF4" s="179"/>
+      <c r="BG4" s="179"/>
+      <c r="BH4" s="179"/>
+      <c r="BI4" s="200"/>
     </row>
     <row r="5" spans="1:65" s="143" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A5" s="233"/>
-      <c r="B5" s="181"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="221"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="182"/>
-      <c r="Q5" s="182"/>
-      <c r="R5" s="183"/>
-      <c r="S5" s="219"/>
-      <c r="T5" s="216"/>
-      <c r="U5" s="216"/>
-      <c r="V5" s="216"/>
-      <c r="W5" s="216"/>
-      <c r="X5" s="216"/>
-      <c r="Y5" s="221"/>
-      <c r="Z5" s="181"/>
-      <c r="AA5" s="182"/>
-      <c r="AB5" s="182"/>
-      <c r="AC5" s="182"/>
-      <c r="AD5" s="183"/>
-      <c r="AE5" s="219"/>
-      <c r="AF5" s="216"/>
-      <c r="AG5" s="216"/>
-      <c r="AH5" s="216"/>
-      <c r="AI5" s="216"/>
-      <c r="AJ5" s="216"/>
-      <c r="AK5" s="221"/>
-      <c r="AL5" s="181"/>
-      <c r="AM5" s="182"/>
-      <c r="AN5" s="182"/>
-      <c r="AO5" s="182"/>
-      <c r="AP5" s="183"/>
-      <c r="AQ5" s="219"/>
-      <c r="AR5" s="216"/>
-      <c r="AS5" s="216"/>
-      <c r="AT5" s="216"/>
-      <c r="AU5" s="216"/>
-      <c r="AV5" s="216"/>
-      <c r="AW5" s="221"/>
-      <c r="AX5" s="181"/>
-      <c r="AY5" s="182"/>
-      <c r="AZ5" s="182"/>
-      <c r="BA5" s="182"/>
-      <c r="BB5" s="183"/>
-      <c r="BC5" s="219"/>
-      <c r="BD5" s="216"/>
-      <c r="BE5" s="216"/>
-      <c r="BF5" s="216"/>
-      <c r="BG5" s="216"/>
-      <c r="BH5" s="216"/>
-      <c r="BI5" s="221"/>
+      <c r="A5" s="197"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="180"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="201"/>
+      <c r="N5" s="234"/>
+      <c r="O5" s="235"/>
+      <c r="P5" s="235"/>
+      <c r="Q5" s="235"/>
+      <c r="R5" s="236"/>
+      <c r="S5" s="178"/>
+      <c r="T5" s="180"/>
+      <c r="U5" s="180"/>
+      <c r="V5" s="180"/>
+      <c r="W5" s="180"/>
+      <c r="X5" s="180"/>
+      <c r="Y5" s="201"/>
+      <c r="Z5" s="234"/>
+      <c r="AA5" s="235"/>
+      <c r="AB5" s="235"/>
+      <c r="AC5" s="235"/>
+      <c r="AD5" s="236"/>
+      <c r="AE5" s="178"/>
+      <c r="AF5" s="180"/>
+      <c r="AG5" s="180"/>
+      <c r="AH5" s="180"/>
+      <c r="AI5" s="180"/>
+      <c r="AJ5" s="180"/>
+      <c r="AK5" s="201"/>
+      <c r="AL5" s="234"/>
+      <c r="AM5" s="235"/>
+      <c r="AN5" s="235"/>
+      <c r="AO5" s="235"/>
+      <c r="AP5" s="236"/>
+      <c r="AQ5" s="178"/>
+      <c r="AR5" s="180"/>
+      <c r="AS5" s="180"/>
+      <c r="AT5" s="180"/>
+      <c r="AU5" s="180"/>
+      <c r="AV5" s="180"/>
+      <c r="AW5" s="201"/>
+      <c r="AX5" s="234"/>
+      <c r="AY5" s="235"/>
+      <c r="AZ5" s="235"/>
+      <c r="BA5" s="235"/>
+      <c r="BB5" s="236"/>
+      <c r="BC5" s="178"/>
+      <c r="BD5" s="180"/>
+      <c r="BE5" s="180"/>
+      <c r="BF5" s="180"/>
+      <c r="BG5" s="180"/>
+      <c r="BH5" s="180"/>
+      <c r="BI5" s="201"/>
     </row>
     <row r="6" spans="1:65" s="23" customFormat="1" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A6" s="233"/>
-      <c r="B6" s="184"/>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="221"/>
-      <c r="N6" s="184"/>
-      <c r="O6" s="185"/>
-      <c r="P6" s="185"/>
-      <c r="Q6" s="185"/>
-      <c r="R6" s="186"/>
-      <c r="S6" s="219"/>
-      <c r="T6" s="216"/>
-      <c r="U6" s="216"/>
-      <c r="V6" s="216"/>
-      <c r="W6" s="216"/>
-      <c r="X6" s="216"/>
-      <c r="Y6" s="221"/>
-      <c r="Z6" s="187"/>
-      <c r="AA6" s="188"/>
-      <c r="AB6" s="188"/>
-      <c r="AC6" s="188"/>
-      <c r="AD6" s="189"/>
-      <c r="AE6" s="219"/>
-      <c r="AF6" s="216"/>
-      <c r="AG6" s="216"/>
-      <c r="AH6" s="216"/>
-      <c r="AI6" s="216"/>
-      <c r="AJ6" s="216"/>
-      <c r="AK6" s="221"/>
-      <c r="AL6" s="184"/>
-      <c r="AM6" s="185"/>
-      <c r="AN6" s="185"/>
-      <c r="AO6" s="185"/>
-      <c r="AP6" s="186"/>
-      <c r="AQ6" s="219"/>
-      <c r="AR6" s="216"/>
-      <c r="AS6" s="216"/>
-      <c r="AT6" s="216"/>
-      <c r="AU6" s="216"/>
-      <c r="AV6" s="216"/>
-      <c r="AW6" s="221"/>
-      <c r="AX6" s="184"/>
-      <c r="AY6" s="185"/>
-      <c r="AZ6" s="185"/>
-      <c r="BA6" s="185"/>
-      <c r="BB6" s="186"/>
-      <c r="BC6" s="219"/>
-      <c r="BD6" s="216"/>
-      <c r="BE6" s="216"/>
-      <c r="BF6" s="216"/>
-      <c r="BG6" s="216"/>
-      <c r="BH6" s="216"/>
-      <c r="BI6" s="221"/>
+      <c r="A6" s="197"/>
+      <c r="B6" s="203"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="180"/>
+      <c r="I6" s="180"/>
+      <c r="J6" s="180"/>
+      <c r="K6" s="180"/>
+      <c r="L6" s="180"/>
+      <c r="M6" s="201"/>
+      <c r="N6" s="203"/>
+      <c r="O6" s="204"/>
+      <c r="P6" s="204"/>
+      <c r="Q6" s="204"/>
+      <c r="R6" s="205"/>
+      <c r="S6" s="178"/>
+      <c r="T6" s="180"/>
+      <c r="U6" s="180"/>
+      <c r="V6" s="180"/>
+      <c r="W6" s="180"/>
+      <c r="X6" s="180"/>
+      <c r="Y6" s="201"/>
+      <c r="Z6" s="203"/>
+      <c r="AA6" s="204"/>
+      <c r="AB6" s="204"/>
+      <c r="AC6" s="204"/>
+      <c r="AD6" s="205"/>
+      <c r="AE6" s="178"/>
+      <c r="AF6" s="180"/>
+      <c r="AG6" s="180"/>
+      <c r="AH6" s="180"/>
+      <c r="AI6" s="180"/>
+      <c r="AJ6" s="180"/>
+      <c r="AK6" s="201"/>
+      <c r="AL6" s="203"/>
+      <c r="AM6" s="204"/>
+      <c r="AN6" s="204"/>
+      <c r="AO6" s="204"/>
+      <c r="AP6" s="205"/>
+      <c r="AQ6" s="178"/>
+      <c r="AR6" s="180"/>
+      <c r="AS6" s="180"/>
+      <c r="AT6" s="180"/>
+      <c r="AU6" s="180"/>
+      <c r="AV6" s="180"/>
+      <c r="AW6" s="201"/>
+      <c r="AX6" s="203"/>
+      <c r="AY6" s="204"/>
+      <c r="AZ6" s="204"/>
+      <c r="BA6" s="204"/>
+      <c r="BB6" s="205"/>
+      <c r="BC6" s="178"/>
+      <c r="BD6" s="180"/>
+      <c r="BE6" s="180"/>
+      <c r="BF6" s="180"/>
+      <c r="BG6" s="180"/>
+      <c r="BH6" s="180"/>
+      <c r="BI6" s="201"/>
     </row>
     <row r="7" spans="1:65" s="54" customFormat="1" ht="24.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="234"/>
+      <c r="A7" s="198"/>
       <c r="B7" s="69" t="s">
         <v>109</v>
       </c>
@@ -5644,10 +5629,10 @@
       <c r="G7" s="136"/>
       <c r="H7" s="137"/>
       <c r="I7" s="137"/>
-      <c r="J7" s="217"/>
-      <c r="K7" s="217"/>
-      <c r="L7" s="217"/>
-      <c r="M7" s="222"/>
+      <c r="J7" s="199"/>
+      <c r="K7" s="199"/>
+      <c r="L7" s="199"/>
+      <c r="M7" s="202"/>
       <c r="N7" s="138" t="s">
         <v>109</v>
       </c>
@@ -5666,10 +5651,10 @@
       <c r="S7" s="136"/>
       <c r="T7" s="137"/>
       <c r="U7" s="137"/>
-      <c r="V7" s="217"/>
-      <c r="W7" s="217"/>
-      <c r="X7" s="217"/>
-      <c r="Y7" s="222"/>
+      <c r="V7" s="199"/>
+      <c r="W7" s="199"/>
+      <c r="X7" s="199"/>
+      <c r="Y7" s="202"/>
       <c r="Z7" s="69" t="s">
         <v>109</v>
       </c>
@@ -5688,10 +5673,10 @@
       <c r="AE7" s="136"/>
       <c r="AF7" s="137"/>
       <c r="AG7" s="137"/>
-      <c r="AH7" s="217"/>
-      <c r="AI7" s="217"/>
-      <c r="AJ7" s="217"/>
-      <c r="AK7" s="222"/>
+      <c r="AH7" s="199"/>
+      <c r="AI7" s="199"/>
+      <c r="AJ7" s="199"/>
+      <c r="AK7" s="202"/>
       <c r="AL7" s="69" t="s">
         <v>109</v>
       </c>
@@ -5710,10 +5695,10 @@
       <c r="AQ7" s="136"/>
       <c r="AR7" s="137"/>
       <c r="AS7" s="137"/>
-      <c r="AT7" s="217"/>
-      <c r="AU7" s="217"/>
-      <c r="AV7" s="217"/>
-      <c r="AW7" s="222"/>
+      <c r="AT7" s="199"/>
+      <c r="AU7" s="199"/>
+      <c r="AV7" s="199"/>
+      <c r="AW7" s="202"/>
       <c r="AX7" s="69" t="s">
         <v>109</v>
       </c>
@@ -5732,13 +5717,13 @@
       <c r="BC7" s="136"/>
       <c r="BD7" s="137"/>
       <c r="BE7" s="137"/>
-      <c r="BF7" s="217"/>
-      <c r="BG7" s="217"/>
-      <c r="BH7" s="217"/>
-      <c r="BI7" s="222"/>
+      <c r="BF7" s="199"/>
+      <c r="BG7" s="199"/>
+      <c r="BH7" s="199"/>
+      <c r="BI7" s="202"/>
     </row>
     <row r="8" spans="1:65" s="56" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A8" s="201" t="s">
+      <c r="A8" s="211" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="127"/>
@@ -5820,7 +5805,7 @@
       <c r="BI8" s="79"/>
     </row>
     <row r="9" spans="1:65" s="56" customFormat="1" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A9" s="202"/>
+      <c r="A9" s="212"/>
       <c r="B9" s="128" t="str">
         <f>IF(OR(E8="",E9=""),"",E9/E8)</f>
         <v/>
@@ -5915,7 +5900,7 @@
       <c r="BI9" s="81"/>
     </row>
     <row r="10" spans="1:65" ht="37.5" customHeight="1">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="213" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="149" t="str">
@@ -6015,7 +6000,7 @@
       </c>
     </row>
     <row r="11" spans="1:65" s="56" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A11" s="204"/>
+      <c r="A11" s="214"/>
       <c r="B11" s="173" t="str">
         <f>IF(OR(E10="",E11=""),"",E11/E10)</f>
         <v/>
@@ -6110,7 +6095,7 @@
       <c r="BI11" s="87"/>
     </row>
     <row r="12" spans="1:65" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A12" s="205"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="172" t="str">
         <f t="shared" ref="B12:B25" si="5">IF(OR(E11="",E12=""),"",E12/E11)</f>
         <v/>
@@ -6205,7 +6190,7 @@
       <c r="BI12" s="81"/>
     </row>
     <row r="13" spans="1:65" ht="37.5" customHeight="1">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="216" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="149" t="str">
@@ -6302,7 +6287,7 @@
       <c r="BI13" s="79"/>
     </row>
     <row r="14" spans="1:65" ht="37.5" customHeight="1">
-      <c r="A14" s="207"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="173" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6397,7 +6382,7 @@
       <c r="BI14" s="85"/>
     </row>
     <row r="15" spans="1:65" s="56" customFormat="1" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A15" s="208"/>
+      <c r="A15" s="218"/>
       <c r="B15" s="172" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6492,7 +6477,7 @@
       <c r="BI15" s="89"/>
     </row>
     <row r="16" spans="1:65" ht="37.5" customHeight="1">
-      <c r="A16" s="209" t="s">
+      <c r="A16" s="219" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="149" t="str">
@@ -6589,7 +6574,7 @@
       <c r="BI16" s="79"/>
     </row>
     <row r="17" spans="1:61" ht="37.5" customHeight="1">
-      <c r="A17" s="210"/>
+      <c r="A17" s="220"/>
       <c r="B17" s="173" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6684,7 +6669,7 @@
       <c r="BI17" s="87"/>
     </row>
     <row r="18" spans="1:61" s="56" customFormat="1" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A18" s="211"/>
+      <c r="A18" s="221"/>
       <c r="B18" s="172" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6779,7 +6764,7 @@
       <c r="BI18" s="81"/>
     </row>
     <row r="19" spans="1:61" s="56" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A19" s="212" t="s">
+      <c r="A19" s="222" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="149" t="str">
@@ -6876,7 +6861,7 @@
       <c r="BI19" s="79"/>
     </row>
     <row r="20" spans="1:61" ht="37.5" customHeight="1">
-      <c r="A20" s="213"/>
+      <c r="A20" s="223"/>
       <c r="B20" s="173" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6971,7 +6956,7 @@
       <c r="BI20" s="85"/>
     </row>
     <row r="21" spans="1:61" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A21" s="214"/>
+      <c r="A21" s="224"/>
       <c r="B21" s="172" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -7066,7 +7051,7 @@
       <c r="BI21" s="89"/>
     </row>
     <row r="22" spans="1:61" ht="37.5" customHeight="1">
-      <c r="A22" s="196" t="s">
+      <c r="A22" s="206" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="149" t="str">
@@ -7161,7 +7146,7 @@
       <c r="BI22" s="79"/>
     </row>
     <row r="23" spans="1:61" ht="37.5" customHeight="1">
-      <c r="A23" s="197"/>
+      <c r="A23" s="207"/>
       <c r="B23" s="173" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -7254,7 +7239,7 @@
       <c r="BI23" s="85"/>
     </row>
     <row r="24" spans="1:61" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A24" s="198"/>
+      <c r="A24" s="208"/>
       <c r="B24" s="172" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -7496,12 +7481,12 @@
       <c r="BI26" s="2"/>
     </row>
     <row r="27" spans="1:61" ht="20.25" thickBot="1">
-      <c r="A27" s="199" t="s">
+      <c r="A27" s="209" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="200"/>
-      <c r="C27" s="200"/>
-      <c r="D27" s="200"/>
+      <c r="B27" s="210"/>
+      <c r="C27" s="210"/>
+      <c r="D27" s="210"/>
       <c r="E27" s="62" t="e">
         <f>AVERAGE(E8:E25)</f>
         <v>#DIV/0!</v>
@@ -7577,65 +7562,65 @@
     </row>
     <row r="28" spans="1:61" ht="22.5" thickBot="1"/>
     <row r="29" spans="1:61">
-      <c r="E29" s="193" t="s">
+      <c r="E29" s="188" t="s">
         <v>110</v>
       </c>
-      <c r="F29" s="194"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="194"/>
-      <c r="I29" s="194"/>
-      <c r="J29" s="194"/>
-      <c r="K29" s="194"/>
-      <c r="L29" s="194"/>
-      <c r="M29" s="195"/>
+      <c r="F29" s="189"/>
+      <c r="G29" s="189"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="189"/>
+      <c r="J29" s="189"/>
+      <c r="K29" s="189"/>
+      <c r="L29" s="189"/>
+      <c r="M29" s="190"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="193" t="s">
+      <c r="Q29" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="R29" s="194"/>
-      <c r="S29" s="194"/>
-      <c r="T29" s="194"/>
-      <c r="U29" s="194"/>
-      <c r="V29" s="194"/>
-      <c r="W29" s="194"/>
-      <c r="X29" s="194"/>
-      <c r="Y29" s="195"/>
+      <c r="R29" s="189"/>
+      <c r="S29" s="189"/>
+      <c r="T29" s="189"/>
+      <c r="U29" s="189"/>
+      <c r="V29" s="189"/>
+      <c r="W29" s="189"/>
+      <c r="X29" s="189"/>
+      <c r="Y29" s="190"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="193" t="s">
+      <c r="AC29" s="188" t="s">
         <v>112</v>
       </c>
-      <c r="AD29" s="194"/>
-      <c r="AE29" s="194"/>
-      <c r="AF29" s="194"/>
-      <c r="AG29" s="194"/>
-      <c r="AH29" s="194"/>
-      <c r="AI29" s="194"/>
-      <c r="AJ29" s="194"/>
-      <c r="AK29" s="195"/>
+      <c r="AD29" s="189"/>
+      <c r="AE29" s="189"/>
+      <c r="AF29" s="189"/>
+      <c r="AG29" s="189"/>
+      <c r="AH29" s="189"/>
+      <c r="AI29" s="189"/>
+      <c r="AJ29" s="189"/>
+      <c r="AK29" s="190"/>
       <c r="AN29" s="8"/>
-      <c r="AO29" s="193" t="s">
+      <c r="AO29" s="188" t="s">
         <v>115</v>
       </c>
-      <c r="AP29" s="194"/>
-      <c r="AQ29" s="194"/>
-      <c r="AR29" s="194"/>
-      <c r="AS29" s="194"/>
-      <c r="AT29" s="194"/>
-      <c r="AU29" s="194"/>
-      <c r="AV29" s="194"/>
-      <c r="AW29" s="195"/>
+      <c r="AP29" s="189"/>
+      <c r="AQ29" s="189"/>
+      <c r="AR29" s="189"/>
+      <c r="AS29" s="189"/>
+      <c r="AT29" s="189"/>
+      <c r="AU29" s="189"/>
+      <c r="AV29" s="189"/>
+      <c r="AW29" s="190"/>
       <c r="AZ29" s="8"/>
-      <c r="BA29" s="193" t="s">
+      <c r="BA29" s="188" t="s">
         <v>113</v>
       </c>
-      <c r="BB29" s="194"/>
-      <c r="BC29" s="194"/>
-      <c r="BD29" s="194"/>
-      <c r="BE29" s="194"/>
-      <c r="BF29" s="194"/>
-      <c r="BG29" s="194"/>
-      <c r="BH29" s="194"/>
-      <c r="BI29" s="195"/>
+      <c r="BB29" s="189"/>
+      <c r="BC29" s="189"/>
+      <c r="BD29" s="189"/>
+      <c r="BE29" s="189"/>
+      <c r="BF29" s="189"/>
+      <c r="BG29" s="189"/>
+      <c r="BH29" s="189"/>
+      <c r="BI29" s="190"/>
     </row>
     <row r="30" spans="1:61">
       <c r="E30" s="16">
@@ -7644,9 +7629,9 @@
       <c r="F30" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="G30" s="190"/>
-      <c r="H30" s="191"/>
-      <c r="I30" s="192"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="226"/>
+      <c r="I30" s="227"/>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
       <c r="L30" s="15"/>
@@ -7658,9 +7643,9 @@
       <c r="R30" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="S30" s="190"/>
-      <c r="T30" s="191"/>
-      <c r="U30" s="192"/>
+      <c r="S30" s="225"/>
+      <c r="T30" s="226"/>
+      <c r="U30" s="227"/>
       <c r="V30" s="15"/>
       <c r="W30" s="15"/>
       <c r="X30" s="15"/>
@@ -7672,9 +7657,9 @@
       <c r="AD30" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="AE30" s="190"/>
-      <c r="AF30" s="191"/>
-      <c r="AG30" s="192"/>
+      <c r="AE30" s="225"/>
+      <c r="AF30" s="226"/>
+      <c r="AG30" s="227"/>
       <c r="AH30" s="15"/>
       <c r="AI30" s="15"/>
       <c r="AJ30" s="15"/>
@@ -7686,9 +7671,9 @@
       <c r="AP30" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="AQ30" s="190"/>
-      <c r="AR30" s="191"/>
-      <c r="AS30" s="192"/>
+      <c r="AQ30" s="225"/>
+      <c r="AR30" s="226"/>
+      <c r="AS30" s="227"/>
       <c r="AT30" s="15"/>
       <c r="AU30" s="15"/>
       <c r="AV30" s="15"/>
@@ -7700,9 +7685,9 @@
       <c r="BB30" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="BC30" s="190"/>
-      <c r="BD30" s="191"/>
-      <c r="BE30" s="192"/>
+      <c r="BC30" s="225"/>
+      <c r="BD30" s="226"/>
+      <c r="BE30" s="227"/>
       <c r="BF30" s="15"/>
       <c r="BG30" s="15"/>
       <c r="BH30" s="15"/>
@@ -7715,9 +7700,9 @@
       <c r="F31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G31" s="190"/>
-      <c r="H31" s="191"/>
-      <c r="I31" s="192"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="226"/>
+      <c r="I31" s="227"/>
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
       <c r="L31" s="15"/>
@@ -7729,9 +7714,9 @@
       <c r="R31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="S31" s="190"/>
-      <c r="T31" s="191"/>
-      <c r="U31" s="192"/>
+      <c r="S31" s="225"/>
+      <c r="T31" s="226"/>
+      <c r="U31" s="227"/>
       <c r="V31" s="15"/>
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
@@ -7743,9 +7728,9 @@
       <c r="AD31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="AE31" s="190"/>
-      <c r="AF31" s="191"/>
-      <c r="AG31" s="192"/>
+      <c r="AE31" s="225"/>
+      <c r="AF31" s="226"/>
+      <c r="AG31" s="227"/>
       <c r="AH31" s="15"/>
       <c r="AI31" s="15"/>
       <c r="AJ31" s="15"/>
@@ -7757,9 +7742,9 @@
       <c r="AP31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="AQ31" s="190"/>
-      <c r="AR31" s="191"/>
-      <c r="AS31" s="192"/>
+      <c r="AQ31" s="225"/>
+      <c r="AR31" s="226"/>
+      <c r="AS31" s="227"/>
       <c r="AT31" s="15"/>
       <c r="AU31" s="15"/>
       <c r="AV31" s="15"/>
@@ -7771,9 +7756,9 @@
       <c r="BB31" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="BC31" s="190"/>
-      <c r="BD31" s="191"/>
-      <c r="BE31" s="192"/>
+      <c r="BC31" s="225"/>
+      <c r="BD31" s="226"/>
+      <c r="BE31" s="227"/>
       <c r="BF31" s="15"/>
       <c r="BG31" s="15"/>
       <c r="BH31" s="15"/>
@@ -7786,9 +7771,9 @@
       <c r="F32" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="G32" s="190"/>
-      <c r="H32" s="191"/>
-      <c r="I32" s="192"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="226"/>
+      <c r="I32" s="227"/>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
       <c r="L32" s="15"/>
@@ -7800,9 +7785,9 @@
       <c r="R32" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="S32" s="190"/>
-      <c r="T32" s="191"/>
-      <c r="U32" s="192"/>
+      <c r="S32" s="225"/>
+      <c r="T32" s="226"/>
+      <c r="U32" s="227"/>
       <c r="V32" s="15"/>
       <c r="W32" s="15"/>
       <c r="X32" s="15"/>
@@ -7814,9 +7799,9 @@
       <c r="AD32" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="AE32" s="190"/>
-      <c r="AF32" s="191"/>
-      <c r="AG32" s="192"/>
+      <c r="AE32" s="225"/>
+      <c r="AF32" s="226"/>
+      <c r="AG32" s="227"/>
       <c r="AH32" s="15"/>
       <c r="AI32" s="15"/>
       <c r="AJ32" s="15"/>
@@ -7828,9 +7813,9 @@
       <c r="AP32" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="AQ32" s="190"/>
-      <c r="AR32" s="191"/>
-      <c r="AS32" s="192"/>
+      <c r="AQ32" s="225"/>
+      <c r="AR32" s="226"/>
+      <c r="AS32" s="227"/>
       <c r="AT32" s="15"/>
       <c r="AU32" s="15"/>
       <c r="AV32" s="15"/>
@@ -7842,9 +7827,9 @@
       <c r="BB32" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BC32" s="190"/>
-      <c r="BD32" s="191"/>
-      <c r="BE32" s="192"/>
+      <c r="BC32" s="225"/>
+      <c r="BD32" s="226"/>
+      <c r="BE32" s="227"/>
       <c r="BF32" s="15"/>
       <c r="BG32" s="15"/>
       <c r="BH32" s="15"/>
@@ -7857,9 +7842,9 @@
       <c r="F33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="G33" s="190"/>
-      <c r="H33" s="191"/>
-      <c r="I33" s="192"/>
+      <c r="G33" s="225"/>
+      <c r="H33" s="226"/>
+      <c r="I33" s="227"/>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
       <c r="L33" s="15"/>
@@ -7871,9 +7856,9 @@
       <c r="R33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="S33" s="190"/>
-      <c r="T33" s="191"/>
-      <c r="U33" s="192"/>
+      <c r="S33" s="225"/>
+      <c r="T33" s="226"/>
+      <c r="U33" s="227"/>
       <c r="V33" s="15"/>
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
@@ -7885,9 +7870,9 @@
       <c r="AD33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AE33" s="190"/>
-      <c r="AF33" s="191"/>
-      <c r="AG33" s="192"/>
+      <c r="AE33" s="225"/>
+      <c r="AF33" s="226"/>
+      <c r="AG33" s="227"/>
       <c r="AH33" s="15"/>
       <c r="AI33" s="15"/>
       <c r="AJ33" s="15"/>
@@ -7899,9 +7884,9 @@
       <c r="AP33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AQ33" s="190"/>
-      <c r="AR33" s="191"/>
-      <c r="AS33" s="192"/>
+      <c r="AQ33" s="225"/>
+      <c r="AR33" s="226"/>
+      <c r="AS33" s="227"/>
       <c r="AT33" s="15"/>
       <c r="AU33" s="15"/>
       <c r="AV33" s="15"/>
@@ -7913,9 +7898,9 @@
       <c r="BB33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="BC33" s="190"/>
-      <c r="BD33" s="191"/>
-      <c r="BE33" s="192"/>
+      <c r="BC33" s="225"/>
+      <c r="BD33" s="226"/>
+      <c r="BE33" s="227"/>
       <c r="BF33" s="15"/>
       <c r="BG33" s="15"/>
       <c r="BH33" s="15"/>
@@ -7928,9 +7913,9 @@
       <c r="F34" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="190"/>
-      <c r="H34" s="191"/>
-      <c r="I34" s="192"/>
+      <c r="G34" s="225"/>
+      <c r="H34" s="226"/>
+      <c r="I34" s="227"/>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
       <c r="L34" s="15"/>
@@ -7942,9 +7927,9 @@
       <c r="R34" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="S34" s="190"/>
-      <c r="T34" s="191"/>
-      <c r="U34" s="192"/>
+      <c r="S34" s="225"/>
+      <c r="T34" s="226"/>
+      <c r="U34" s="227"/>
       <c r="V34" s="15"/>
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
@@ -7956,9 +7941,9 @@
       <c r="AD34" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AE34" s="190"/>
-      <c r="AF34" s="191"/>
-      <c r="AG34" s="192"/>
+      <c r="AE34" s="225"/>
+      <c r="AF34" s="226"/>
+      <c r="AG34" s="227"/>
       <c r="AH34" s="15"/>
       <c r="AI34" s="15"/>
       <c r="AJ34" s="15"/>
@@ -7970,9 +7955,9 @@
       <c r="AP34" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AQ34" s="190"/>
-      <c r="AR34" s="191"/>
-      <c r="AS34" s="192"/>
+      <c r="AQ34" s="225"/>
+      <c r="AR34" s="226"/>
+      <c r="AS34" s="227"/>
       <c r="AT34" s="15"/>
       <c r="AU34" s="15"/>
       <c r="AV34" s="15"/>
@@ -7984,9 +7969,9 @@
       <c r="BB34" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="BC34" s="190"/>
-      <c r="BD34" s="191"/>
-      <c r="BE34" s="192"/>
+      <c r="BC34" s="225"/>
+      <c r="BD34" s="226"/>
+      <c r="BE34" s="227"/>
       <c r="BF34" s="15"/>
       <c r="BG34" s="15"/>
       <c r="BH34" s="15"/>
@@ -7999,9 +7984,9 @@
       <c r="F35" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="G35" s="175"/>
-      <c r="H35" s="176"/>
-      <c r="I35" s="177"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="230"/>
       <c r="J35" s="76"/>
       <c r="K35" s="76"/>
       <c r="L35" s="76"/>
@@ -8013,9 +7998,9 @@
       <c r="R35" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="S35" s="175"/>
-      <c r="T35" s="176"/>
-      <c r="U35" s="177"/>
+      <c r="S35" s="228"/>
+      <c r="T35" s="229"/>
+      <c r="U35" s="230"/>
       <c r="V35" s="76"/>
       <c r="W35" s="76"/>
       <c r="X35" s="76"/>
@@ -8027,9 +8012,9 @@
       <c r="AD35" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="AE35" s="175"/>
-      <c r="AF35" s="176"/>
-      <c r="AG35" s="177"/>
+      <c r="AE35" s="228"/>
+      <c r="AF35" s="229"/>
+      <c r="AG35" s="230"/>
       <c r="AH35" s="76"/>
       <c r="AI35" s="76"/>
       <c r="AJ35" s="76"/>
@@ -8041,9 +8026,9 @@
       <c r="AP35" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="AQ35" s="175"/>
-      <c r="AR35" s="176"/>
-      <c r="AS35" s="177"/>
+      <c r="AQ35" s="228"/>
+      <c r="AR35" s="229"/>
+      <c r="AS35" s="230"/>
       <c r="AT35" s="76"/>
       <c r="AU35" s="76"/>
       <c r="AV35" s="76"/>
@@ -8055,9 +8040,9 @@
       <c r="BB35" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="BC35" s="175"/>
-      <c r="BD35" s="176"/>
-      <c r="BE35" s="177"/>
+      <c r="BC35" s="228"/>
+      <c r="BD35" s="229"/>
+      <c r="BE35" s="230"/>
       <c r="BF35" s="76"/>
       <c r="BG35" s="76"/>
       <c r="BH35" s="76"/>
@@ -8104,16 +8089,76 @@
     </sortState>
   </autoFilter>
   <mergeCells count="104">
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="S4:S6"/>
-    <mergeCell ref="T4:T6"/>
-    <mergeCell ref="U4:U6"/>
-    <mergeCell ref="AE4:AE6"/>
-    <mergeCell ref="AF4:AF6"/>
-    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="BC35:BE35"/>
+    <mergeCell ref="N4:R4"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="N5:R5"/>
+    <mergeCell ref="N6:R6"/>
+    <mergeCell ref="Z4:AD4"/>
+    <mergeCell ref="Z5:AD5"/>
+    <mergeCell ref="Z6:AD6"/>
+    <mergeCell ref="AL4:AP4"/>
+    <mergeCell ref="AL5:AP5"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="AX4:BB4"/>
+    <mergeCell ref="AX5:BB5"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BC31:BE31"/>
+    <mergeCell ref="BC32:BE32"/>
+    <mergeCell ref="BC33:BE33"/>
+    <mergeCell ref="BC34:BE34"/>
+    <mergeCell ref="AE35:AG35"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ31:AS31"/>
+    <mergeCell ref="AQ32:AS32"/>
+    <mergeCell ref="AQ33:AS33"/>
+    <mergeCell ref="AQ34:AS34"/>
+    <mergeCell ref="AQ35:AS35"/>
+    <mergeCell ref="AE30:AG30"/>
+    <mergeCell ref="AE31:AG31"/>
+    <mergeCell ref="AE32:AG32"/>
+    <mergeCell ref="AE33:AG33"/>
+    <mergeCell ref="AE34:AG34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="S30:U30"/>
+    <mergeCell ref="S31:U31"/>
+    <mergeCell ref="S32:U32"/>
+    <mergeCell ref="S33:U33"/>
+    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="S35:U35"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="AO29:AW29"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="Q29:Y29"/>
+    <mergeCell ref="AC29:AK29"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="BG4:BG7"/>
+    <mergeCell ref="AQ4:AQ6"/>
+    <mergeCell ref="AR4:AR6"/>
+    <mergeCell ref="AS4:AS6"/>
+    <mergeCell ref="BC4:BC6"/>
+    <mergeCell ref="BD4:BD6"/>
+    <mergeCell ref="BE4:BE6"/>
+    <mergeCell ref="BH4:BH7"/>
+    <mergeCell ref="BI4:BI7"/>
+    <mergeCell ref="AW4:AW7"/>
+    <mergeCell ref="BF4:BF7"/>
+    <mergeCell ref="AT4:AT7"/>
+    <mergeCell ref="AU4:AU7"/>
+    <mergeCell ref="AV4:AV7"/>
+    <mergeCell ref="AX6:BB6"/>
     <mergeCell ref="AG4:AG6"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="A2:E2"/>
@@ -8138,76 +8183,16 @@
     <mergeCell ref="AH4:AH7"/>
     <mergeCell ref="AI4:AI7"/>
     <mergeCell ref="AJ4:AJ7"/>
-    <mergeCell ref="BG4:BG7"/>
-    <mergeCell ref="AQ4:AQ6"/>
-    <mergeCell ref="AR4:AR6"/>
-    <mergeCell ref="AS4:AS6"/>
-    <mergeCell ref="BC4:BC6"/>
-    <mergeCell ref="BD4:BD6"/>
-    <mergeCell ref="BE4:BE6"/>
-    <mergeCell ref="BH4:BH7"/>
-    <mergeCell ref="BI4:BI7"/>
-    <mergeCell ref="AW4:AW7"/>
-    <mergeCell ref="BF4:BF7"/>
-    <mergeCell ref="AT4:AT7"/>
-    <mergeCell ref="AU4:AU7"/>
-    <mergeCell ref="AV4:AV7"/>
-    <mergeCell ref="AX6:BB6"/>
-    <mergeCell ref="AO29:AW29"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="Q29:Y29"/>
-    <mergeCell ref="AC29:AK29"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="AQ33:AS33"/>
-    <mergeCell ref="AQ34:AS34"/>
-    <mergeCell ref="AQ35:AS35"/>
-    <mergeCell ref="AE30:AG30"/>
-    <mergeCell ref="AE31:AG31"/>
-    <mergeCell ref="AE32:AG32"/>
-    <mergeCell ref="AE33:AG33"/>
-    <mergeCell ref="AE34:AG34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="S30:U30"/>
-    <mergeCell ref="S31:U31"/>
-    <mergeCell ref="S32:U32"/>
-    <mergeCell ref="S33:U33"/>
-    <mergeCell ref="S34:U34"/>
-    <mergeCell ref="S35:U35"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="BC35:BE35"/>
-    <mergeCell ref="N4:R4"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="N5:R5"/>
-    <mergeCell ref="N6:R6"/>
-    <mergeCell ref="Z4:AD4"/>
-    <mergeCell ref="Z5:AD5"/>
-    <mergeCell ref="Z6:AD6"/>
-    <mergeCell ref="AL4:AP4"/>
-    <mergeCell ref="AL5:AP5"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="AX4:BB4"/>
-    <mergeCell ref="AX5:BB5"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BC31:BE31"/>
-    <mergeCell ref="BC32:BE32"/>
-    <mergeCell ref="BC33:BE33"/>
-    <mergeCell ref="BC34:BE34"/>
-    <mergeCell ref="AE35:AG35"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ31:AS31"/>
-    <mergeCell ref="AQ32:AS32"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="S4:S6"/>
+    <mergeCell ref="T4:T6"/>
+    <mergeCell ref="U4:U6"/>
+    <mergeCell ref="AE4:AE6"/>
+    <mergeCell ref="AF4:AF6"/>
+    <mergeCell ref="F2:N2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B8:B25 N8:N25 Z8:Z25 AL8:AL25 AX8:AX25">
